--- a/forms/trg/Formulir_TRG_aisrg.xlsx
+++ b/forms/trg/Formulir_TRG_aisrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B28)</f>
+        <f>COUNTA(Anggota!B5:B29)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F28)</f>
+        <f>COUNTA(Anggota!F5:F29)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,17 +913,13 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Andi Emelda, S.P., M.Si.</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
+          <t>Prof. Dr. Ir. Sitti Bulkis, M.S.</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Agricultural Institutions, Gender, and Food Security</t>
         </is>
       </c>
       <c r="E5" s="11" t="n"/>
@@ -933,15 +929,19 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0009-0004-5988-0708</t>
+          <t>0000-0002-9207-9953</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6991111</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="n"/>
+          <t>6005362</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57202444377</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Ridwan, S.TP., M.Sc, Ph.D</t>
+          <t>Andi Emelda, S.P., M.Si.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -974,19 +974,15 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5453-6052</t>
+          <t>0009-0004-5988-0708</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6990837</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>57217207630</t>
-        </is>
-      </c>
+          <t>6991111</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -999,12 +995,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ir. A. Amrullah, M.Si</t>
+          <t>Muhammad Ridwan, S.TP., M.Sc, Ph.D</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1012,28 +1008,24 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>Socio-economics of agriculture</t>
-        </is>
-      </c>
+      <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-4633-8520</t>
+          <t>0000-0001-5453-6052</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6014348</t>
+          <t>6990837</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57202443313</t>
+          <t>57217207630</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1048,12 +1040,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Rahmadanih, M.Si</t>
+          <t>Ir. A. Amrullah, M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1061,24 +1053,28 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n"/>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Socio-economics of agriculture</t>
+        </is>
+      </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7179-0498</t>
+          <t>0000-0002-4633-8520</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6005393</t>
+          <t>6014348</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57202443125</t>
+          <t>57202443313</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1093,12 +1089,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Idris Summase, M.Si.</t>
+          <t>Prof. Dr. Ir. Rahmadanih, M.Si</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1106,28 +1102,24 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Agricultural Sociology, Agricultural Development</t>
-        </is>
-      </c>
+      <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-0649-2419</t>
+          <t>0000-0002-7179-0498</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>6018976</t>
+          <t>6005393</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57212147611</t>
+          <t>57202443125</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1142,12 +1134,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Adhyta Puspita S., S.P., M.Si</t>
+          <t>Dr. Ir. Idris Summase, M.Si.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1157,7 +1149,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Entrepreneurship, Agribusiness Management and Food Security</t>
+          <t>Agricultural Sociology, Agricultural Development</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1166,17 +1158,17 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0009-0006-6469-7654</t>
+          <t>0000-0002-0649-2419</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6931179</t>
+          <t>6018976</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57226573071</t>
+          <t>57212147611</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1191,12 +1183,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Muhammad Arsyad, Ph.D</t>
+          <t>Adhyta Puspita S., S.P., M.Si</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1206,7 +1198,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Economics and Rural Development</t>
+          <t>Entrepreneurship, Agribusiness Management and Food Security</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1215,17 +1207,17 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5619-4543</t>
+          <t>0009-0006-6469-7654</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>6029217</t>
+          <t>6931179</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>57202770024</t>
+          <t>57226573071</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1240,22 +1232,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Prof. B. Nishantha, Ph.D.</t>
+          <t>Prof. Muhammad Arsyad, Ph.D</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>University of Colombo</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Business Institutions and Social Entrepreneurship</t>
+          <t>Agricultural Economics and Rural Development</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1264,13 +1256,17 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8274-9880</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="n"/>
+          <t>0000-0001-5619-4543</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>6029217</t>
+        </is>
+      </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>56258366000</t>
+          <t>57202770024</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1285,22 +1281,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Simon Anthony Kayombo</t>
+          <t>Prof. B. Nishantha, Ph.D.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>National Chung Hsing University (NCHU), Taiwan</t>
+          <t>University of Colombo</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Extension Systems</t>
+          <t>Agricultural Business Institutions and Social Entrepreneurship</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1309,13 +1305,13 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-4284-7053</t>
+          <t>0000-0001-8274-9880</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/58106727300</t>
+          <t>56258366000</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1330,22 +1326,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Andi Aulia Fadillah</t>
+          <t>Simon Anthony Kayombo</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researcher</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>National Chung Hsing University (NCHU), Taiwan</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Socio-Economy</t>
+          <t>Agricultural Extension Systems</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1354,15 +1350,15 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-6045-9847</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>6951433</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="n"/>
+          <t>0000-0002-4284-7053</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/authors/58106727300</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1375,12 +1371,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Rasdiana Mudatsir</t>
+          <t>Andi Aulia Fadillah</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1390,7 +1386,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>s and Food Security</t>
+          <t>Agricultural Socio-Economy</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1399,12 +1395,12 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5242-4962</t>
+          <t>0000-0002-6045-9847</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>6198141</t>
+          <t>6951433</t>
         </is>
       </c>
       <c r="L15" s="12" t="n"/>
@@ -1420,12 +1416,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Wulandari</t>
+          <t>Rasdiana Mudatsir</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1435,7 +1431,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>socio-economic</t>
+          <t>s and Food Security</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1444,10 +1440,14 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>0009-0009-3958-0173</t>
-        </is>
-      </c>
-      <c r="K16" s="12" t="n"/>
+          <t>0000-0001-5242-4962</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>6198141</t>
+        </is>
+      </c>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
@@ -1459,18 +1459,42 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="11" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Wulandari</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>socio-economic</t>
+        </is>
+      </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>0009-0009-3958-0173</t>
+        </is>
+      </c>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1659,15 +1683,32 @@
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="12" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_aisrg.xlsx
+++ b/forms/trg/Formulir_TRG_aisrg.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Ir. Sitti Bulkis, M.S.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Agricultural Institutions, Gender, and Food Security</t>
